--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -1495,7 +1495,7 @@
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>💡 手順3〜8のグラフ・表・見出しの差し替えは、Pythonツール make_teirei.py でまとめて自動化もできます（末尾の付録を参照）。コメント記入と最終保存は引き続き手作業です。</t>
+          <t>【ポイント】手順3〜8のグラフ・表・見出しの差し替えは、Pythonツール make_teirei.py でまとめて自動化もできます（末尾の付録を参照）。コメント記入と最終保存は引き続き手作業です。</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
     <row r="46">
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>▲ 保存先フォルダ</t>
+          <t>図：保存先フォルダ</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <row r="52">
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 月度の書き換えは最初に。後で表示やコメントを書くときに月がずれないようにするためです。</t>
+          <t>【注意】月度の書き換えは最初に。後で表示やコメントを書くときに月がずれないようにするためです。</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
     <row r="77">
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>▲ 完成イメージ（スライド3）</t>
+          <t>図：完成イメージ（スライド3）</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
     <row r="95">
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>▲ 1日平均シート</t>
+          <t>図：1日平均シート</t>
         </is>
       </c>
     </row>
@@ -1621,14 +1621,14 @@
     <row r="100">
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>⚠️ なぜ先に？ 1日平均 シートは別タブの「日報（件数）貼り付け用」と連携（数式参照）しています。先に値へ固定しておかないと、次の貼り付けで数式が壊れたり表示が崩れたりするためです。</t>
+          <t>【注意】なぜ先に？ 1日平均 シートは別タブの「日報（件数）貼り付け用」と連携（数式参照）しています。先に値へ固定しておかないと、次の貼り付けで数式が壊れたり表示が崩れたりするためです。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>▲ タブ：日報貼り付け用と1日平均</t>
+          <t>図：タブ：日報貼り付け用と1日平均</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
     <row r="136">
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>▲ 日報貼り付け用タブ</t>
+          <t>図：日報貼り付け用タブ</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
     <row r="162">
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>▲ 日報に当月分を貼付</t>
+          <t>図：日報に当月分を貼付</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
     <row r="190">
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>▲ 1日平均グラフ更新</t>
+          <t>図：1日平均グラフ更新</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
     <row r="215">
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>▲ PPTにグラフを貼付</t>
+          <t>図：PPTにグラフを貼付</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
     <row r="248">
       <c r="B248" s="7" t="inlineStr">
         <is>
-          <t>▲ 日別処理：土日含む</t>
+          <t>図：日別処理：土日含む</t>
         </is>
       </c>
     </row>
@@ -1761,14 +1761,14 @@
     <row r="270">
       <c r="B270" s="7" t="inlineStr">
         <is>
-          <t>▲ 日別処理：稼働日のみ</t>
+          <t>図：日別処理：稼働日のみ</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 「0件だから消す」ではなく「土日祝だから消す」で判断してください。稼働日でもたまたま全項目が0の日があり、0かどうかで消すとその日が抜けてしまいます。</t>
+          <t>【注意】「0件だから消す」ではなく「土日祝だから消す」で判断してください。稼働日でもたまたま全項目が0の日があり、0かどうかで消すとその日が抜けてしまいます。</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
     <row r="295">
       <c r="B295" s="7" t="inlineStr">
         <is>
-          <t>▲ 日報の分析コメント欄</t>
+          <t>図：日報の分析コメント欄</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
     <row r="320">
       <c r="B320" s="7" t="inlineStr">
         <is>
-          <t>▲ スライド4：日別処理</t>
+          <t>図：スライド4：日別処理</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
     <row r="353">
       <c r="B353" s="7" t="inlineStr">
         <is>
-          <t>▲ 八神Excelの場所</t>
+          <t>図：八神Excelの場所</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
     <row r="379">
       <c r="B379" s="7" t="inlineStr">
         <is>
-          <t>▲ 八神：月別タブ</t>
+          <t>図：八神：月別タブ</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
     <row r="410">
       <c r="B410" s="7" t="inlineStr">
         <is>
-          <t>▲ 八神sellout集計：当月</t>
+          <t>図：八神sellout集計：当月</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
     <row r="415">
       <c r="B415" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 空欄のままだとグラフや合計に正しく反映されません。一括 の行を当月の全稼働日ぶん 0 で埋めて隙間をなくします。</t>
+          <t>【注意】空欄のままだとグラフや合計に正しく反映されません。一括 の行を当月の全稼働日ぶん 0 で埋めて隙間をなくします。</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="B446" s="7" t="inlineStr">
         <is>
-          <t>▲ 八神：一括行に0を入力</t>
+          <t>図：八神：一括行に0を入力</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
     <row r="474">
       <c r="B474" s="7" t="inlineStr">
         <is>
-          <t>▲ スライド5：八神 完成</t>
+          <t>図：スライド5：八神 完成</t>
         </is>
       </c>
     </row>
@@ -1943,21 +1943,21 @@
     <row r="500">
       <c r="B500" s="7" t="inlineStr">
         <is>
-          <t>▲ Outlook：八神件数集計</t>
+          <t>図：Outlook：八神件数集計</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="B502" s="5" t="inlineStr">
         <is>
-          <t>💬 件数が「9件」などになっている場合、その理由はこのメールで確認できます（多い月は背景を紐解いておくとコメントが書きやすくなります）。</t>
+          <t>【補足】件数が「9件」などになっている場合、その理由はこのメールで確認できます（多い月は背景を紐解いておくとコメントが書きやすくなります）。</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="B525" s="7" t="inlineStr">
         <is>
-          <t>▲ Outlook：八神内訳確認</t>
+          <t>図：Outlook：八神内訳確認</t>
         </is>
       </c>
     </row>
@@ -1992,14 +1992,14 @@
     <row r="559">
       <c r="B559" s="7" t="inlineStr">
         <is>
-          <t>▲ サポートグラフ</t>
+          <t>図：サポートグラフ</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="B561" s="5" t="inlineStr">
         <is>
-          <t>📝 用語の補足：「返却通知書（代理）」は、正式には「返却・使用通知書」というタイトルの書類です。該当データはメールブランチの後ろにあります。</t>
+          <t>【用語】「返却通知書（代理）」は、正式には「返却・使用通知書」というタイトルの書類です。該当データはメールブランチの後ろにあります。</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
     <row r="587">
       <c r="B587" s="7" t="inlineStr">
         <is>
-          <t>▲ スライド6：サポート</t>
+          <t>図：スライド6：サポート</t>
         </is>
       </c>
     </row>
@@ -2055,14 +2055,14 @@
     <row r="624">
       <c r="B624" s="7" t="inlineStr">
         <is>
-          <t>▲ メール依頼シート</t>
+          <t>図：メール依頼シート</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="B626" s="5" t="inlineStr">
         <is>
-          <t>💬 メール依頼（✉）について：ここは原則いじるものはありません。集計は関さんがまとめてくれています。件数が多いときは「なぜ多いのか？」を紐解いておく必要があります。</t>
+          <t>【補足】メール依頼について：ここは原則いじるものはありません。集計は関さんがまとめてくれています。件数が多いときは「なぜ多いのか？」を紐解いておく必要があります。</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
     <row r="653">
       <c r="B653" s="7" t="inlineStr">
         <is>
-          <t>▲ Outlook：メール依頼</t>
+          <t>図：Outlook：メール依頼</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
     <row r="690">
       <c r="B690" s="7" t="inlineStr">
         <is>
-          <t>▲ 受発信：元データ</t>
+          <t>図：受発信：元データ</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
     <row r="718">
       <c r="B718" s="7" t="inlineStr">
         <is>
-          <t>▲ 電話タブ：前月状態</t>
+          <t>図：電話タブ：前月状態</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
     <row r="744">
       <c r="B744" s="7" t="inlineStr">
         <is>
-          <t>▲ 電話タブ：当月貼付</t>
+          <t>図：電話タブ：当月貼付</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
     <row r="775">
       <c r="B775" s="7" t="inlineStr">
         <is>
-          <t>▲ 電話：平均算出と集計表</t>
+          <t>図：電話：平均算出と集計表</t>
         </is>
       </c>
     </row>
@@ -2209,21 +2209,21 @@
     <row r="801">
       <c r="B801" s="7" t="inlineStr">
         <is>
-          <t>▲ PPT電話：軸調整1</t>
+          <t>図：PPT電話：軸調整1</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="B803" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 縦軸の最大値を月に合わせて手調整します。件数に応じて、70件以下の月なら最大を50にするなど、見やすい高さに直してください。</t>
+          <t>【注意】縦軸の最大値を月に合わせて手調整します。件数に応じて、70件以下の月なら最大を50にするなど、見やすい高さに直してください。</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="B826" s="7" t="inlineStr">
         <is>
-          <t>▲ PPT電話：軸調整2</t>
+          <t>図：PPT電話：軸調整2</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
     <row r="852">
       <c r="B852" s="7" t="inlineStr">
         <is>
-          <t>▲ スライド8：電話完成</t>
+          <t>図：スライド8：電話完成</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
     <row r="881">
       <c r="B881" s="7" t="inlineStr">
         <is>
-          <t>▲ ネットワーク保存ダイアログ</t>
+          <t>図：ネットワーク保存ダイアログ</t>
         </is>
       </c>
     </row>

--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -1733,7 +1733,7 @@
     <row r="224" ht="22" customHeight="1">
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>4-1. 稼働日だけにする（土日祝の0列を消す）</t>
+          <t>4-1. 稼働日だけにする（土日祝の0列を非表示にする）</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
     <row r="250">
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>土日祝（0件）の列を削除して、平日（稼働日）だけのグラフにします。</t>
+          <t>土日祝（0件）の列を非表示にして、平日（稼働日）だけのグラフにします。※ 列は削除せず非表示にします（元データは残したまま、グラフの見た目だけ整えます）。</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
     <row r="272">
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>【注意】「0件だから消す」ではなく「土日祝だから消す」で判断してください。稼働日でもたまたま全項目が0の日があり、0かどうかで消すとその日が抜けてしまいます。</t>
+          <t>【注意】「0件だから非表示」ではなく「土日祝だから非表示」で判断してください。稼働日でもたまたま全項目が0の日があり、0かどうかで非表示にするとその日が抜けてしまいます。</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="C889" s="4" t="inlineStr">
         <is>
-          <t>日別グラフは土日祝（0件）の列を削除。「0だから消す」ではなく「土日祝だから消す」。</t>
+          <t>日別グラフは土日祝（0件）の列を非表示（削除しない）。「0だから非表示」ではなく「土日祝だから非表示」。</t>
         </is>
       </c>
     </row>

--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -298,7 +298,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="1238250"/>
@@ -323,7 +323,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3943350"/>
@@ -348,7 +348,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>138</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4171950"/>
@@ -373,7 +373,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>166</row>
+      <row>167</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4010025"/>
@@ -398,7 +398,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>192</row>
+      <row>193</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3914775"/>
@@ -423,7 +423,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>226</row>
+      <row>227</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3686175"/>
@@ -448,7 +448,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>250</row>
+      <row>251</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3419475"/>
@@ -473,7 +473,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>275</row>
+      <row>276</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3390900"/>
@@ -498,7 +498,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>297</row>
+      <row>298</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3857625"/>
@@ -523,7 +523,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>329</row>
+      <row>330</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4171950"/>
@@ -548,7 +548,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>355</row>
+      <row>356</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4114800"/>
@@ -573,7 +573,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>381</row>
+      <row>382</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="5143500"/>
@@ -598,7 +598,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>415</row>
+      <row>416</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="5457825"/>
@@ -623,7 +623,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>450</row>
+      <row>451</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4029075"/>
@@ -648,7 +648,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>478</row>
+      <row>479</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3771900"/>
@@ -673,7 +673,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>502</row>
+      <row>503</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3943350"/>
@@ -698,7 +698,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>533</row>
+      <row>534</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4391025"/>
@@ -723,7 +723,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>564</row>
+      <row>565</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3914775"/>
@@ -748,7 +748,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>595</row>
+      <row>596</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="5076825"/>
@@ -773,7 +773,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>629</row>
+      <row>630</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4076700"/>
@@ -798,7 +798,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>664</row>
+      <row>665</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4391025"/>
@@ -823,7 +823,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>694</row>
+      <row>695</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4162425"/>
@@ -848,7 +848,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>720</row>
+      <row>721</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4086225"/>
@@ -873,7 +873,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>748</row>
+      <row>749</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4581525"/>
@@ -898,7 +898,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>779</row>
+      <row>780</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3676650"/>
@@ -923,7 +923,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>803</row>
+      <row>804</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3886200"/>
@@ -948,7 +948,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>828</row>
+      <row>829</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4105275"/>
@@ -973,7 +973,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>859</row>
+      <row>860</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3800475"/>
@@ -1286,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F909"/>
+  <dimension ref="B2:F910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1619,860 +1619,844 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>【数式 ▶ 値 の変換手順】
+1. 当月列を選択してコピー（Ctrl + C）
+2. 選択したまま、同じ列の上で右クリックし、「貼り付けのオプション」から「値」（クリップボードに 123 が付いたアイコン）を選ぶ
+   ※ または、右クリック →「形式を選択して貼り付け」→「値」→ OK
+3. セルの中身が数式（=…）ではなく数値そのものになっていれば完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>【注意】なぜ先に？ 1日平均 シートは別タブの「日報（件数）貼り付け用」と連携（数式参照）しています。先に値へ固定しておかないと、次の貼り付けで数式が壊れたり表示が崩れたりするためです。</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="7" t="inlineStr">
+    <row r="110">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>図：タブ：日報貼り付け用と1日平均</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="22" customHeight="1">
-      <c r="B111" s="8" t="inlineStr">
+    <row r="112" ht="22" customHeight="1">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>3-3. 「日報（件数）貼り付け用」に当月分を貼り付ける</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>横にある「日報（件数）貼り付け用」タブをクリックし、SharePointからコピーした当月分を、すべてコピー＆ペーストで貼り付けます。これが大元のデータになります。</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="B136" s="7" t="inlineStr">
+    <row r="137">
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>図：日報貼り付け用タブ</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="B138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>貼り付け後、当月の行（処理件数）が反映されます。</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="B162" s="7" t="inlineStr">
+    <row r="163">
+      <c r="B163" s="7" t="inlineStr">
         <is>
           <t>図：日報に当月分を貼付</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="B164" s="8" t="inlineStr">
+    <row r="165" ht="22" customHeight="1">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>3-4. グラフをPowerPointへ</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="B166" s="2" t="inlineStr">
+    <row r="167">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>1日平均 シートのグラフが当月データで自動更新されるので、内容を確認します。</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="B190" s="7" t="inlineStr">
+    <row r="191">
+      <c r="B191" s="7" t="inlineStr">
         <is>
           <t>図：1日平均グラフ更新</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="B192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>更新されたグラフをスライド3にコピーして貼り付けます。</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="B215" s="7" t="inlineStr">
+    <row r="216">
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t>図：PPTにグラフを貼付</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="22" customHeight="1">
-      <c r="B217" s="8" t="inlineStr">
+    <row r="218" ht="22" customHeight="1">
+      <c r="B218" s="8" t="inlineStr">
         <is>
           <t>3-5. コメントを書く</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="B219" s="2" t="inlineStr">
+    <row r="220">
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>「・前月に比べて、短期・長期の処理件数が増加」のように、前月比の気づきを1〜2行で記入します。</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="30" customHeight="1">
-      <c r="B221" s="1" t="inlineStr">
+    <row r="222" ht="30" customHeight="1">
+      <c r="B222" s="1" t="inlineStr">
         <is>
           <t>4. スライド4：日別処理件数</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="B223" s="2" t="inlineStr">
+    <row r="224">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>当月の稼働日ごとの処理件数を、積み上げ棒グラフで表示します。</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="22" customHeight="1">
-      <c r="B224" s="8" t="inlineStr">
+    <row r="225" ht="22" customHeight="1">
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>4-1. 稼働日だけにする（土日祝の0列を非表示にする）</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="B226" s="2" t="inlineStr">
+    <row r="227">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>新）日別処理 のグラフは、初期状態では土日も含めて全日付が入っています（土日は0件）。</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="B248" s="7" t="inlineStr">
+    <row r="249">
+      <c r="B249" s="7" t="inlineStr">
         <is>
           <t>図：日別処理：土日含む</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="B250" s="2" t="inlineStr">
+    <row r="251">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>土日祝（0件）の列を非表示にして、平日（稼働日）だけのグラフにします。※ 列は削除せず非表示にします（元データは残したまま、グラフの見た目だけ整えます）。</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="B270" s="7" t="inlineStr">
+    <row r="271">
+      <c r="B271" s="7" t="inlineStr">
         <is>
           <t>図：日別処理：稼働日のみ</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="B272" s="5" t="inlineStr">
+    <row r="273">
+      <c r="B273" s="5" t="inlineStr">
         <is>
           <t>【注意】「0件だから非表示」ではなく「土日祝だから非表示」で判断してください。稼働日でもたまたま全項目が0の日があり、0かどうかで非表示にするとその日が抜けてしまいます。</t>
         </is>
       </c>
     </row>
-    <row r="273" ht="22" customHeight="1">
-      <c r="B273" s="8" t="inlineStr">
+    <row r="274" ht="22" customHeight="1">
+      <c r="B274" s="8" t="inlineStr">
         <is>
           <t>4-2. コメントとPowerPoint反映</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="B275" s="2" t="inlineStr">
+    <row r="276">
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>日報のコメント欄を参考に、当月の特記事項を確認します。</t>
         </is>
       </c>
     </row>
-    <row r="295">
-      <c r="B295" s="7" t="inlineStr">
+    <row r="296">
+      <c r="B296" s="7" t="inlineStr">
         <is>
           <t>図：日報の分析コメント欄</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="B297" s="2" t="inlineStr">
+    <row r="298">
+      <c r="B298" s="2" t="inlineStr">
         <is>
           <t>グラフをスライド4へコピーし、コメントを記入します。</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="B320" s="7" t="inlineStr">
+    <row r="321">
+      <c r="B321" s="7" t="inlineStr">
         <is>
           <t>図：スライド4：日別処理</t>
         </is>
       </c>
     </row>
-    <row r="323" ht="30" customHeight="1">
-      <c r="B323" s="1" t="inlineStr">
+    <row r="324" ht="30" customHeight="1">
+      <c r="B324" s="1" t="inlineStr">
         <is>
           <t>5. スライド5：八神セルアウト</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="B325" s="2" t="inlineStr">
+    <row r="326">
+      <c r="B326" s="2" t="inlineStr">
         <is>
           <t>八神向けの当月セルアウト（一括／買取／長期／短期）を集計します。</t>
         </is>
       </c>
     </row>
-    <row r="326" ht="22" customHeight="1">
-      <c r="B326" s="8" t="inlineStr">
+    <row r="327" ht="22" customHeight="1">
+      <c r="B327" s="8" t="inlineStr">
         <is>
           <t>5-1. 八神sellout集計ファイルを開く</t>
         </is>
       </c>
     </row>
-    <row r="328">
-      <c r="B328" s="2" t="inlineStr">
+    <row r="329">
+      <c r="B329" s="2" t="inlineStr">
         <is>
           <t>八神のExcelは、ネットワークの次の場所にあります。</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="B329" s="6" t="inlineStr">
+    <row r="330">
+      <c r="B330" s="6" t="inlineStr">
         <is>
           <t>ネットワーク &gt; fscwork &gt; Tokyo &gt; 10_セルアウト &gt; 八神セルアウト &gt; ★八神sellout集計2026年度.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="B353" s="7" t="inlineStr">
+    <row r="354">
+      <c r="B354" s="7" t="inlineStr">
         <is>
           <t>図：八神Excelの場所</t>
         </is>
       </c>
     </row>
-    <row r="355">
-      <c r="B355" s="2" t="inlineStr">
+    <row r="356">
+      <c r="B356" s="2" t="inlineStr">
         <is>
           <t>このファイルを開き、当月タブ（例：2026.5）を選びます。タブは月ごとに分かれています。</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="B379" s="7" t="inlineStr">
+    <row r="380">
+      <c r="B380" s="7" t="inlineStr">
         <is>
           <t>図：八神：月別タブ</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="B381" s="2" t="inlineStr">
+    <row r="382">
+      <c r="B382" s="2" t="inlineStr">
         <is>
           <t>当月タブにデータが入っていることと、グラフが更新されていることを確認します。</t>
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="B410" s="7" t="inlineStr">
+    <row r="411">
+      <c r="B411" s="7" t="inlineStr">
         <is>
           <t>図：八神sellout集計：当月</t>
         </is>
       </c>
     </row>
-    <row r="412" ht="22" customHeight="1">
-      <c r="B412" s="8" t="inlineStr">
+    <row r="413" ht="22" customHeight="1">
+      <c r="B413" s="8" t="inlineStr">
         <is>
           <t>5-2. 「一括」行の空欄に手動で 0 を入れる</t>
         </is>
       </c>
     </row>
-    <row r="414">
-      <c r="B414" s="2" t="inlineStr">
+    <row r="415">
+      <c r="B415" s="2" t="inlineStr">
         <is>
           <t>一括 の行は、値のある日（例：24・21・30・31）だけが入っていて、それ以外の日は空欄になっています。この空欄のセルすべてに、手動で 0 を入力してください。</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="B415" s="5" t="inlineStr">
+    <row r="416">
+      <c r="B416" s="5" t="inlineStr">
         <is>
           <t>【注意】空欄のままだとグラフや合計に正しく反映されません。一括 の行を当月の全稼働日ぶん 0 で埋めて隙間をなくします。</t>
         </is>
       </c>
     </row>
-    <row r="446">
-      <c r="B446" s="7" t="inlineStr">
+    <row r="447">
+      <c r="B447" s="7" t="inlineStr">
         <is>
           <t>図：八神：一括行に0を入力</t>
         </is>
       </c>
     </row>
-    <row r="448" ht="22" customHeight="1">
-      <c r="B448" s="8" t="inlineStr">
+    <row r="449" ht="22" customHeight="1">
+      <c r="B449" s="8" t="inlineStr">
         <is>
           <t>5-3. グラフをPowerPointへ</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="B450" s="2" t="inlineStr">
+    <row r="451">
+      <c r="B451" s="2" t="inlineStr">
         <is>
           <t>0 を埋めたら、当月グラフを選択してスライド5へコピーします。</t>
         </is>
       </c>
     </row>
-    <row r="474">
-      <c r="B474" s="7" t="inlineStr">
+    <row r="475">
+      <c r="B475" s="7" t="inlineStr">
         <is>
           <t>図：スライド5：八神 完成</t>
         </is>
       </c>
     </row>
-    <row r="476" ht="22" customHeight="1">
-      <c r="B476" s="8" t="inlineStr">
+    <row r="477" ht="22" customHeight="1">
+      <c r="B477" s="8" t="inlineStr">
         <is>
           <t>5-4. 件数の根拠はOutlookで確認</t>
         </is>
       </c>
     </row>
-    <row r="478">
-      <c r="B478" s="2" t="inlineStr">
+    <row r="479">
+      <c r="B479" s="2" t="inlineStr">
         <is>
           <t>八神の件数は Outlookのメールから集計しています。件数が多い・少ないと感じたら、該当メールを開いて内訳（理由）を確認できます。</t>
         </is>
       </c>
     </row>
-    <row r="500">
-      <c r="B500" s="7" t="inlineStr">
+    <row r="501">
+      <c r="B501" s="7" t="inlineStr">
         <is>
           <t>図：Outlook：八神件数集計</t>
         </is>
       </c>
     </row>
-    <row r="502">
-      <c r="B502" s="5" t="inlineStr">
+    <row r="503">
+      <c r="B503" s="5" t="inlineStr">
         <is>
           <t>【補足】件数が「9件」などになっている場合、その理由はこのメールで確認できます（多い月は背景を紐解いておくとコメントが書きやすくなります）。</t>
         </is>
       </c>
     </row>
-    <row r="525">
-      <c r="B525" s="7" t="inlineStr">
+    <row r="526">
+      <c r="B526" s="7" t="inlineStr">
         <is>
           <t>図：Outlook：八神内訳確認</t>
         </is>
       </c>
     </row>
-    <row r="528" ht="30" customHeight="1">
-      <c r="B528" s="1" t="inlineStr">
+    <row r="529" ht="30" customHeight="1">
+      <c r="B529" s="1" t="inlineStr">
         <is>
           <t>6. スライド6：サポート業務</t>
         </is>
       </c>
     </row>
-    <row r="530">
-      <c r="B530" s="2" t="inlineStr">
+    <row r="531">
+      <c r="B531" s="2" t="inlineStr">
         <is>
           <t>サポート業務（補充・使用報告書／返却通知書 ×2／サンプル／赤伝）の当月件数を表示します。</t>
         </is>
       </c>
     </row>
-    <row r="531" ht="22" customHeight="1">
-      <c r="B531" s="8" t="inlineStr">
+    <row r="532" ht="22" customHeight="1">
+      <c r="B532" s="8" t="inlineStr">
         <is>
           <t>6-1. サポートグラフファイルを開く</t>
         </is>
       </c>
     </row>
-    <row r="533">
-      <c r="B533" s="2" t="inlineStr">
+    <row r="534">
+      <c r="B534" s="2" t="inlineStr">
         <is>
           <t>2026年度サポートグラフ.xlsx を開き、当月タブ（例：サポート2026.5）のグラフを確認します。</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="B559" s="7" t="inlineStr">
+    <row r="560">
+      <c r="B560" s="7" t="inlineStr">
         <is>
           <t>図：サポートグラフ</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="B561" s="5" t="inlineStr">
+    <row r="562">
+      <c r="B562" s="5" t="inlineStr">
         <is>
           <t>【用語】「返却通知書（代理）」は、正式には「返却・使用通知書」というタイトルの書類です。該当データはメールブランチの後ろにあります。</t>
         </is>
       </c>
     </row>
-    <row r="562" ht="22" customHeight="1">
-      <c r="B562" s="8" t="inlineStr">
+    <row r="563" ht="22" customHeight="1">
+      <c r="B563" s="8" t="inlineStr">
         <is>
           <t>6-2. グラフをPowerPointへ</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="B564" s="2" t="inlineStr">
+    <row r="565">
+      <c r="B565" s="2" t="inlineStr">
         <is>
           <t>グラフをスライド6へコピーし、コメントを記入します。</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="B587" s="7" t="inlineStr">
+    <row r="588">
+      <c r="B588" s="7" t="inlineStr">
         <is>
           <t>図：スライド6：サポート</t>
         </is>
       </c>
     </row>
-    <row r="590" ht="30" customHeight="1">
-      <c r="B590" s="1" t="inlineStr">
+    <row r="591" ht="30" customHeight="1">
+      <c r="B591" s="1" t="inlineStr">
         <is>
           <t>7. スライド7：メール依頼</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="B592" s="2" t="inlineStr">
+    <row r="593">
+      <c r="B593" s="2" t="inlineStr">
         <is>
           <t>メール依頼（その他／代理店／Cordis本社／営業）の当月件数を表示します。</t>
         </is>
       </c>
     </row>
-    <row r="593" ht="22" customHeight="1">
-      <c r="B593" s="8" t="inlineStr">
+    <row r="594" ht="22" customHeight="1">
+      <c r="B594" s="8" t="inlineStr">
         <is>
           <t>7-1. メール依頼ファイルを開く</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="B595" s="2" t="inlineStr">
+    <row r="596">
+      <c r="B596" s="2" t="inlineStr">
         <is>
           <t>2026年度メール依頼.xlsx を開き、当月タブ（例：メール2026.5）のグラフを確認します。</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="B624" s="7" t="inlineStr">
+    <row r="625">
+      <c r="B625" s="7" t="inlineStr">
         <is>
           <t>図：メール依頼シート</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="B626" s="5" t="inlineStr">
+    <row r="627">
+      <c r="B627" s="5" t="inlineStr">
         <is>
           <t>【補足】メール依頼について：ここは原則いじるものはありません。集計は関さんがまとめてくれています。件数が多いときは「なぜ多いのか？」を紐解いておく必要があります。</t>
         </is>
       </c>
     </row>
-    <row r="627" ht="22" customHeight="1">
-      <c r="B627" s="8" t="inlineStr">
+    <row r="628" ht="22" customHeight="1">
+      <c r="B628" s="8" t="inlineStr">
         <is>
           <t>7-2. 件数の根拠はOutlookで確認</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="B629" s="2" t="inlineStr">
+    <row r="630">
+      <c r="B630" s="2" t="inlineStr">
         <is>
           <t>件数はOutlookで集計しています。必要に応じて該当メールで内訳を確認します。</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="B653" s="7" t="inlineStr">
+    <row r="654">
+      <c r="B654" s="7" t="inlineStr">
         <is>
           <t>図：Outlook：メール依頼</t>
         </is>
       </c>
     </row>
-    <row r="655" ht="22" customHeight="1">
-      <c r="B655" s="8" t="inlineStr">
+    <row r="656" ht="22" customHeight="1">
+      <c r="B656" s="8" t="inlineStr">
         <is>
           <t>7-3. グラフをPowerPointへ</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="B657" s="2" t="inlineStr">
+    <row r="658">
+      <c r="B658" s="2" t="inlineStr">
         <is>
           <t>グラフをスライド7へコピーし、コメントを記入します。</t>
         </is>
       </c>
     </row>
-    <row r="659" ht="30" customHeight="1">
-      <c r="B659" s="1" t="inlineStr">
+    <row r="660" ht="30" customHeight="1">
+      <c r="B660" s="1" t="inlineStr">
         <is>
           <t>8. スライド8：電話応対（グラフ＋右上の集計表）</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="B661" s="2" t="inlineStr">
+    <row r="662">
+      <c r="B662" s="2" t="inlineStr">
         <is>
           <t>当月の日別 受信／発信件数の棒グラフと、右上の集計表（前月比つき）を更新します。</t>
         </is>
       </c>
     </row>
-    <row r="662" ht="22" customHeight="1">
-      <c r="B662" s="8" t="inlineStr">
+    <row r="663" ht="22" customHeight="1">
+      <c r="B663" s="8" t="inlineStr">
         <is>
           <t>8-1. 受発信の元データを用意する</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="B664" s="2" t="inlineStr">
+    <row r="665">
+      <c r="B665" s="2" t="inlineStr">
         <is>
           <t>その月の 202605受発信.xlsx（受信件数／発信件数の日別データ）を開きます。</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="B690" s="7" t="inlineStr">
+    <row r="691">
+      <c r="B691" s="7" t="inlineStr">
         <is>
           <t>図：受発信：元データ</t>
         </is>
       </c>
     </row>
-    <row r="692" ht="22" customHeight="1">
-      <c r="B692" s="8" t="inlineStr">
+    <row r="693" ht="22" customHeight="1">
+      <c r="B693" s="8" t="inlineStr">
         <is>
           <t>8-2. メインExcelの「電話」タブに貼り付ける</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="B694" s="2" t="inlineStr">
+    <row r="695">
+      <c r="B695" s="2" t="inlineStr">
         <is>
           <t>メインExcelの 電話 タブを開きます。貼り付け前は前月のデータが入っています。</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="B718" s="7" t="inlineStr">
+    <row r="719">
+      <c r="B719" s="7" t="inlineStr">
         <is>
           <t>図：電話タブ：前月状態</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="B720" s="2" t="inlineStr">
+    <row r="721">
+      <c r="B721" s="2" t="inlineStr">
         <is>
           <t>受発信データを 電話 タブに貼り付けると、グラフと数値が当月に切り替わります。</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="B744" s="7" t="inlineStr">
+    <row r="745">
+      <c r="B745" s="7" t="inlineStr">
         <is>
           <t>図：電話タブ：当月貼付</t>
         </is>
       </c>
     </row>
-    <row r="746" ht="22" customHeight="1">
-      <c r="B746" s="8" t="inlineStr">
+    <row r="747" ht="22" customHeight="1">
+      <c r="B747" s="8" t="inlineStr">
         <is>
           <t>8-3. 平均と集計表を更新する</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="B748" s="2" t="inlineStr">
+    <row r="749">
+      <c r="B749" s="2" t="inlineStr">
         <is>
           <t>・平均件数＝合計 ÷ 稼働日数（例：=C32/18 のように、合計を稼働日数で割る）で計算します。・右上の集計表（N35:Q38）には、当月・前月・前月比（%）が入ります。</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="B775" s="7" t="inlineStr">
+    <row r="776">
+      <c r="B776" s="7" t="inlineStr">
         <is>
           <t>図：電話：平均算出と集計表</t>
         </is>
       </c>
     </row>
-    <row r="777" ht="22" customHeight="1">
-      <c r="B777" s="8" t="inlineStr">
+    <row r="778" ht="22" customHeight="1">
+      <c r="B778" s="8" t="inlineStr">
         <is>
           <t>8-4. グラフをPowerPointへ（軸の最大値に注意）</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="B779" s="2" t="inlineStr">
+    <row r="780">
+      <c r="B780" s="2" t="inlineStr">
         <is>
           <t>グラフをスライド8へコピーします。</t>
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="B801" s="7" t="inlineStr">
+    <row r="802">
+      <c r="B802" s="7" t="inlineStr">
         <is>
           <t>図：PPT電話：軸調整1</t>
         </is>
       </c>
     </row>
-    <row r="803">
-      <c r="B803" s="5" t="inlineStr">
+    <row r="804">
+      <c r="B804" s="5" t="inlineStr">
         <is>
           <t>【注意】縦軸の最大値を月に合わせて手調整します。件数に応じて、70件以下の月なら最大を50にするなど、見やすい高さに直してください。</t>
         </is>
       </c>
     </row>
-    <row r="826">
-      <c r="B826" s="7" t="inlineStr">
+    <row r="827">
+      <c r="B827" s="7" t="inlineStr">
         <is>
           <t>図：PPT電話：軸調整2</t>
         </is>
       </c>
     </row>
-    <row r="828">
-      <c r="B828" s="2" t="inlineStr">
+    <row r="829">
+      <c r="B829" s="2" t="inlineStr">
         <is>
           <t>集計表も合わせて貼り付け／更新し、コメントを記入すれば完成です。</t>
         </is>
       </c>
     </row>
-    <row r="852">
-      <c r="B852" s="7" t="inlineStr">
+    <row r="853">
+      <c r="B853" s="7" t="inlineStr">
         <is>
           <t>図：スライド8：電話完成</t>
         </is>
       </c>
     </row>
-    <row r="855" ht="30" customHeight="1">
-      <c r="B855" s="1" t="inlineStr">
+    <row r="856" ht="30" customHeight="1">
+      <c r="B856" s="1" t="inlineStr">
         <is>
           <t>9. 仕上げ：保存</t>
         </is>
       </c>
     </row>
-    <row r="857">
-      <c r="B857" s="2" t="inlineStr">
+    <row r="858">
+      <c r="B858" s="2" t="inlineStr">
         <is>
           <t>すべてのスライドを更新し、コメントを記入したら、ネットワークフォルダに保存します。</t>
         </is>
       </c>
     </row>
-    <row r="858">
-      <c r="B858" s="6" t="inlineStr">
+    <row r="859">
+      <c r="B859" s="6" t="inlineStr">
         <is>
           <t>…\16_定例会\2026\</t>
         </is>
       </c>
     </row>
-    <row r="859">
-      <c r="B859" s="2" t="inlineStr">
+    <row r="860">
+      <c r="B860" s="2" t="inlineStr">
         <is>
           <t>・pptx（編集用）と PDF（配布用）の両方で保存します。・ファイル名は コーディスジャパン定例会資料_2026年○月度 の形式に合わせます。</t>
         </is>
       </c>
     </row>
-    <row r="881">
-      <c r="B881" s="7" t="inlineStr">
+    <row r="882">
+      <c r="B882" s="7" t="inlineStr">
         <is>
           <t>図：ネットワーク保存ダイアログ</t>
         </is>
       </c>
     </row>
-    <row r="884" ht="30" customHeight="1">
-      <c r="B884" s="1" t="inlineStr">
+    <row r="885" ht="30" customHeight="1">
+      <c r="B885" s="1" t="inlineStr">
         <is>
           <t>10. つまずきやすいポイント（チェックリスト）</t>
         </is>
       </c>
     </row>
-    <row r="886">
-      <c r="B886" s="3" t="inlineStr">
+    <row r="887">
+      <c r="B887" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C886" s="3" t="inlineStr">
+      <c r="C887" s="3" t="inlineStr">
         <is>
           <t>注意点</t>
-        </is>
-      </c>
-    </row>
-    <row r="887">
-      <c r="B887" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C887" s="4" t="inlineStr">
-        <is>
-          <t>月度の書き換えは最初に。アジェンダ・タイトルの「○月度」を当月へ。</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="B888" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C888" s="4" t="inlineStr">
         <is>
-          <t>1日平均 は 日報（件数）貼り付け用 と連携している。貼り付け前に当月列を数式→値へ固定する。</t>
+          <t>月度の書き換えは最初に。アジェンダ・タイトルの「○月度」を当月へ。</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="B889" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C889" s="4" t="inlineStr">
         <is>
-          <t>日別グラフは土日祝（0件）の列を非表示（削除しない）。「0だから非表示」ではなく「土日祝だから非表示」。</t>
+          <t>1日平均 は 日報（件数）貼り付け用 と連携している。貼り付け前に当月列を数式→値へ固定する。</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="B890" s="4" t="inlineStr">
         <is>
-          <t>3b</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C890" s="4" t="inlineStr">
         <is>
-          <t>八神セルアウトの 一括 行の空欄には手動で 0 を入れる（空欄のままだとグラフ・合計に反映されない）。</t>
+          <t>日別グラフは土日祝（0件）の列を非表示（削除しない）。「0だから非表示」ではなく「土日祝だから非表示」。</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="B891" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3b</t>
         </is>
       </c>
       <c r="C891" s="4" t="inlineStr">
         <is>
-          <t>電話の平均は 合計 ÷ 稼働日数。日数を間違えると平均がずれる。</t>
+          <t>八神セルアウトの 一括 行の空欄には手動で 0 を入れる（空欄のままだとグラフ・合計に反映されない）。</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="B892" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C892" s="4" t="inlineStr">
         <is>
-          <t>電話グラフの縦軸の最大値は手調整（70件以下なら50など）。</t>
+          <t>電話の平均は 合計 ÷ 稼働日数。日数を間違えると平均がずれる。</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="B893" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C893" s="4" t="inlineStr">
         <is>
-          <t>八神・メール・サポートの件数は Outlook側に根拠がある。多い月は理由を確認。</t>
+          <t>電話グラフの縦軸の最大値は手調整（70件以下なら50など）。</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="B894" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C894" s="4" t="inlineStr">
         <is>
-          <t>グラフをPowerPointへ貼るときは、系列の順番・色が崩れていないかを確認（特にスライド3の複合グラフ）。</t>
+          <t>八神・メール・サポートの件数は Outlook側に根拠がある。多い月は理由を確認。</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="B895" s="4" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C895" s="4" t="inlineStr">
+        <is>
+          <t>グラフをPowerPointへ貼るときは、系列の順番・色が崩れていないかを確認（特にスライド3の複合グラフ）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="B896" s="4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C895" s="4" t="inlineStr">
+      <c r="C896" s="4" t="inlineStr">
         <is>
           <t>最後は pptxとPDFの両方をネットワークに保存。</t>
         </is>
       </c>
     </row>
-    <row r="898" ht="30" customHeight="1">
-      <c r="B898" s="1" t="inlineStr">
+    <row r="899" ht="30" customHeight="1">
+      <c r="B899" s="1" t="inlineStr">
         <is>
           <t>付録：データソース対応表</t>
         </is>
       </c>
     </row>
-    <row r="900">
-      <c r="B900" s="3" t="inlineStr">
+    <row r="901">
+      <c r="B901" s="3" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="C900" s="3" t="inlineStr">
+      <c r="C901" s="3" t="inlineStr">
         <is>
           <t>グラフ／表</t>
         </is>
       </c>
-      <c r="D900" s="3" t="inlineStr">
+      <c r="D901" s="3" t="inlineStr">
         <is>
           <t>元ファイル</t>
         </is>
       </c>
-      <c r="E900" s="3" t="inlineStr">
+      <c r="E901" s="3" t="inlineStr">
         <is>
           <t>シート</t>
         </is>
       </c>
-      <c r="F900" s="3" t="inlineStr">
+      <c r="F901" s="3" t="inlineStr">
         <is>
           <t>参照範囲・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="901">
-      <c r="B901" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C901" s="4" t="inlineStr">
-        <is>
-          <t>月別1日平均（棒＋折れ線）</t>
-        </is>
-      </c>
-      <c r="D901" s="4" t="inlineStr">
-        <is>
-          <t>メインExcel</t>
-        </is>
-      </c>
-      <c r="E901" s="4" t="inlineStr">
-        <is>
-          <t>1日平均</t>
-        </is>
-      </c>
-      <c r="F901" s="4" t="inlineStr">
-        <is>
-          <t>行2〜10、直近13ヶ月。横軸＝日付(yyyy-mm)</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="B902" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C902" s="4" t="inlineStr">
         <is>
-          <t>日別処理（積み上げ棒）</t>
+          <t>月別1日平均（棒＋折れ線）</t>
         </is>
       </c>
       <c r="D902" s="4" t="inlineStr">
@@ -2482,280 +2466,308 @@
       </c>
       <c r="E902" s="4" t="inlineStr">
         <is>
-          <t>新）日別処理</t>
+          <t>1日平均</t>
         </is>
       </c>
       <c r="F902" s="4" t="inlineStr">
         <is>
-          <t>行3〜7。稼働日のみ。横軸＝日付＋曜日</t>
+          <t>行2〜10、直近13ヶ月。横軸＝日付(yyyy-mm)</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="B903" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C903" s="4" t="inlineStr">
         <is>
-          <t>八神セルアウト</t>
+          <t>日別処理（積み上げ棒）</t>
         </is>
       </c>
       <c r="D903" s="4" t="inlineStr">
         <is>
-          <t>★八神sellout集計</t>
+          <t>メインExcel</t>
         </is>
       </c>
       <c r="E903" s="4" t="inlineStr">
         <is>
-          <t>2026.5 等</t>
+          <t>新）日別処理</t>
         </is>
       </c>
       <c r="F903" s="4" t="inlineStr">
         <is>
-          <t>行3〜6（一括/買取/長期/短期）。件数はOutlook集計</t>
+          <t>行3〜7。稼働日のみ。横軸＝日付＋曜日</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="B904" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C904" s="4" t="inlineStr">
         <is>
-          <t>サポート業務</t>
+          <t>八神セルアウト</t>
         </is>
       </c>
       <c r="D904" s="4" t="inlineStr">
         <is>
-          <t>2026年度サポートグラフ</t>
+          <t>★八神sellout集計</t>
         </is>
       </c>
       <c r="E904" s="4" t="inlineStr">
         <is>
-          <t>サポート2026.5 等</t>
+          <t>2026.5 等</t>
         </is>
       </c>
       <c r="F904" s="4" t="inlineStr">
         <is>
-          <t>行3〜7（補充・使用報告書/返却通知書×2/サンプル/赤伝）</t>
+          <t>行3〜6（一括/買取/長期/短期）。件数はOutlook集計</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="B905" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C905" s="4" t="inlineStr">
         <is>
-          <t>メール依頼</t>
+          <t>サポート業務</t>
         </is>
       </c>
       <c r="D905" s="4" t="inlineStr">
         <is>
-          <t>2026年度メール依頼</t>
+          <t>2026年度サポートグラフ</t>
         </is>
       </c>
       <c r="E905" s="4" t="inlineStr">
         <is>
-          <t>メール2026.5 等</t>
+          <t>サポート2026.5 等</t>
         </is>
       </c>
       <c r="F905" s="4" t="inlineStr">
         <is>
-          <t>行3〜6（その他/代理店/Cordis本社/営業）。件数はOutlook集計</t>
+          <t>行3〜7（補充・使用報告書/返却通知書×2/サンプル/赤伝）</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="B906" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C906" s="4" t="inlineStr">
         <is>
-          <t>電話応対（棒）＋集計表</t>
+          <t>メール依頼</t>
         </is>
       </c>
       <c r="D906" s="4" t="inlineStr">
         <is>
-          <t>メインExcel</t>
+          <t>2026年度メール依頼</t>
         </is>
       </c>
       <c r="E906" s="4" t="inlineStr">
         <is>
-          <t>電話</t>
+          <t>メール2026.5 等</t>
         </is>
       </c>
       <c r="F906" s="4" t="inlineStr">
         <is>
-          <t>グラフ:C/D列、表:N35:Q38。元データ=202605受発信.xlsx</t>
+          <t>行3〜6（その他/代理店/Cordis本社/営業）。件数はOutlook集計</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="B907" s="4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C907" s="4" t="inlineStr">
+        <is>
+          <t>電話応対（棒）＋集計表</t>
+        </is>
+      </c>
+      <c r="D907" s="4" t="inlineStr">
+        <is>
+          <t>メインExcel</t>
+        </is>
+      </c>
+      <c r="E907" s="4" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="F907" s="4" t="inlineStr">
+        <is>
+          <t>グラフ:C/D列、表:N35:Q38。元データ=202605受発信.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="B908" s="4" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C907" s="4" t="inlineStr">
+      <c r="C908" s="4" t="inlineStr">
         <is>
           <t>処理ミス（PPM・折れ線）</t>
         </is>
       </c>
-      <c r="D907" s="4" t="inlineStr">
+      <c r="D908" s="4" t="inlineStr">
         <is>
           <t>メインExcel</t>
         </is>
       </c>
-      <c r="E907" s="4" t="inlineStr">
+      <c r="E908" s="4" t="inlineStr">
         <is>
           <t>ミス2024</t>
         </is>
       </c>
-      <c r="F907" s="4" t="inlineStr">
+      <c r="F908" s="4" t="inlineStr">
         <is>
           <t>横軸＝月、系列＝前年/当年</t>
         </is>
       </c>
     </row>
-    <row r="909">
-      <c r="B909" s="5" t="inlineStr">
+    <row r="910">
+      <c r="B910" s="5" t="inlineStr">
         <is>
           <t>祝日：メインExcelの 向う数年の祝日 シートに祝日リストがあり、稼働日の判定に使います。電話の元データ：202605受発信.xlsx を 電話 タブに貼り付けてから使います。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="121">
-    <mergeCell ref="B744:F744"/>
+  <mergeCells count="122">
+    <mergeCell ref="B693:F693"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B528:F528"/>
-    <mergeCell ref="B826:F826"/>
+    <mergeCell ref="B721:F721"/>
+    <mergeCell ref="B276:F276"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B500:F500"/>
     <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B381:F381"/>
-    <mergeCell ref="B592:F592"/>
+    <mergeCell ref="B665:F665"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B779:F779"/>
-    <mergeCell ref="B828:F828"/>
-    <mergeCell ref="B250:F250"/>
-    <mergeCell ref="B328:F328"/>
-    <mergeCell ref="B626:F626"/>
+    <mergeCell ref="B529:F529"/>
+    <mergeCell ref="B827:F827"/>
+    <mergeCell ref="B594:F594"/>
+    <mergeCell ref="B532:F532"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B166:F166"/>
-    <mergeCell ref="B270:F270"/>
-    <mergeCell ref="B410:F410"/>
-    <mergeCell ref="B692:F692"/>
-    <mergeCell ref="B775:F775"/>
+    <mergeCell ref="B691:F691"/>
+    <mergeCell ref="B747:F747"/>
+    <mergeCell ref="B628:F628"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B447:F447"/>
+    <mergeCell ref="B477:F477"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B855:F855"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B694:F694"/>
+    <mergeCell ref="B356:F356"/>
+    <mergeCell ref="B449:F449"/>
+    <mergeCell ref="B654:F654"/>
+    <mergeCell ref="B663:F663"/>
+    <mergeCell ref="B719:F719"/>
+    <mergeCell ref="B227:F227"/>
     <mergeCell ref="B531:F531"/>
-    <mergeCell ref="B355:F355"/>
+    <mergeCell ref="B591:F591"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B662:F662"/>
-    <mergeCell ref="B718:F718"/>
-    <mergeCell ref="B655:F655"/>
-    <mergeCell ref="B720:F720"/>
-    <mergeCell ref="B219:F219"/>
-    <mergeCell ref="B412:F412"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B881:F881"/>
-    <mergeCell ref="B657:F657"/>
-    <mergeCell ref="B803:F803"/>
+    <mergeCell ref="B475:F475"/>
+    <mergeCell ref="B882:F882"/>
+    <mergeCell ref="B167:F167"/>
+    <mergeCell ref="B503:F503"/>
+    <mergeCell ref="B630:F630"/>
+    <mergeCell ref="B853:F853"/>
     <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B852:F852"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B446:F446"/>
-    <mergeCell ref="B525:F525"/>
-    <mergeCell ref="B898:F898"/>
-    <mergeCell ref="B217:F217"/>
+    <mergeCell ref="B780:F780"/>
     <mergeCell ref="B99:F99"/>
-    <mergeCell ref="B448:F448"/>
     <mergeCell ref="B593:F593"/>
-    <mergeCell ref="B664:F664"/>
-    <mergeCell ref="B746:F746"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B658:F658"/>
+    <mergeCell ref="B829:F829"/>
     <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B909:F909"/>
-    <mergeCell ref="B595:F595"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B251:F251"/>
+    <mergeCell ref="B216:F216"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B414:F414"/>
-    <mergeCell ref="B474:F474"/>
-    <mergeCell ref="B659:F659"/>
+    <mergeCell ref="B296:F296"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B109:F109"/>
-    <mergeCell ref="B587:F587"/>
-    <mergeCell ref="B190:F190"/>
-    <mergeCell ref="B295:F295"/>
+    <mergeCell ref="B271:F271"/>
+    <mergeCell ref="B218:F218"/>
+    <mergeCell ref="B411:F411"/>
+    <mergeCell ref="B416:F416"/>
+    <mergeCell ref="B193:F193"/>
+    <mergeCell ref="B321:F321"/>
+    <mergeCell ref="B596:F596"/>
+    <mergeCell ref="B885:F885"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B215:F215"/>
     <mergeCell ref="B273:F273"/>
-    <mergeCell ref="B801:F801"/>
-    <mergeCell ref="B857:F857"/>
+    <mergeCell ref="B749:F749"/>
     <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B323:F323"/>
-    <mergeCell ref="B272:F272"/>
-    <mergeCell ref="B450:F450"/>
-    <mergeCell ref="B748:F748"/>
-    <mergeCell ref="B530:F530"/>
-    <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B856:F856"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B858:F858"/>
-    <mergeCell ref="B559:F559"/>
-    <mergeCell ref="B476:F476"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="B379:F379"/>
-    <mergeCell ref="B478:F478"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B624:F624"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B249:F249"/>
+    <mergeCell ref="B451:F451"/>
+    <mergeCell ref="B534:F534"/>
+    <mergeCell ref="B656:F656"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B413:F413"/>
+    <mergeCell ref="B776:F776"/>
+    <mergeCell ref="B324:F324"/>
+    <mergeCell ref="B899:F899"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B804:F804"/>
+    <mergeCell ref="B222:F222"/>
     <mergeCell ref="B415:F415"/>
-    <mergeCell ref="B884:F884"/>
-    <mergeCell ref="B325:F325"/>
-    <mergeCell ref="B221:F221"/>
-    <mergeCell ref="B561:F561"/>
+    <mergeCell ref="B560:F560"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B110:F110"/>
     <mergeCell ref="B859:F859"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B777:F777"/>
+    <mergeCell ref="B479:F479"/>
+    <mergeCell ref="B380:F380"/>
+    <mergeCell ref="B860:F860"/>
     <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B690:F690"/>
-    <mergeCell ref="B320:F320"/>
+    <mergeCell ref="B327:F327"/>
+    <mergeCell ref="B625:F625"/>
+    <mergeCell ref="B165:F165"/>
+    <mergeCell ref="B910:F910"/>
+    <mergeCell ref="B382:F382"/>
     <mergeCell ref="B326:F326"/>
+    <mergeCell ref="B220:F220"/>
     <mergeCell ref="B562:F562"/>
-    <mergeCell ref="B661:F661"/>
+    <mergeCell ref="B802:F802"/>
     <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B248:F248"/>
-    <mergeCell ref="B297:F297"/>
-    <mergeCell ref="B353:F353"/>
-    <mergeCell ref="B533:F533"/>
-    <mergeCell ref="B653:F653"/>
-    <mergeCell ref="B590:F590"/>
+    <mergeCell ref="B660:F660"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B588:F588"/>
+    <mergeCell ref="B563:F563"/>
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="B354:F354"/>
+    <mergeCell ref="B298:F298"/>
     <mergeCell ref="B329:F329"/>
     <mergeCell ref="B627:F627"/>
     <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B565:F565"/>
+    <mergeCell ref="B745:F745"/>
+    <mergeCell ref="B501:F501"/>
     <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B564:F564"/>
-    <mergeCell ref="B275:F275"/>
-    <mergeCell ref="B502:F502"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B629:F629"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B695:F695"/>
+    <mergeCell ref="B778:F778"/>
+    <mergeCell ref="B330:F330"/>
     <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B526:F526"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -1607,14 +1607,14 @@
     <row r="97" ht="22" customHeight="1">
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>3-2. 先に「1日平均」側の列を数式→値にしておく</t>
+          <t>3-2. 先に前月列（1日平均）を数式→値にしておく</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>メインExcelの 1日平均 シートで、当月列を選択し、数式を「値」に変換しておきます。</t>
+          <t>メインExcelの 1日平均 シートで、前月列（例：5月度を作るなら 2026-04）を選択し、数式を「値」に変換しておきます。（＝前月分の数値を、計算式ではなく確定した数字として固定しておく作業です。）</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       <c r="B100" s="2" t="inlineStr">
         <is>
           <t>【数式 ▶ 値 の変換手順】
-1. 当月列を選択してコピー（Ctrl + C）
+1. 前月列を選択してコピー（Ctrl + C）
 2. 選択したまま、同じ列の上で右クリックし、「貼り付けのオプション」から「値」（クリップボードに 123 が付いたアイコン）を選ぶ
    ※ または、右クリック →「形式を選択して貼り付け」→「値」→ OK
 3. セルの中身が数式（=…）ではなく数値そのものになっていれば完了</t>
@@ -1632,7 +1632,7 @@
     <row r="101">
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>【注意】なぜ先に？ 1日平均 シートは別タブの「日報（件数）貼り付け用」と連携（数式参照）しています。先に値へ固定しておかないと、次の貼り付けで数式が壊れたり表示が崩れたりするためです。</t>
+          <t>【注意】なぜ前月分を先に値にするの？ 1日平均 シートは別タブの「日報（件数）貼り付け用」と連携（数式参照）しています。前月分を値で固定しておかないと、次に当月分を貼り付けたときに前月の数値まで一緒に変わってしまうためです。</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C889" s="4" t="inlineStr">
         <is>
-          <t>1日平均 は 日報（件数）貼り付け用 と連携している。貼り付け前に当月列を数式→値へ固定する。</t>
+          <t>1日平均 は 日報（件数）貼り付け用 と連携している。貼り付け前に前月列を数式→値へ固定する（前月の数値が変わらないように）。</t>
         </is>
       </c>
     </row>

--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -298,7 +298,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="1238250"/>
@@ -323,7 +323,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3943350"/>
@@ -348,7 +348,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>139</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4171950"/>
@@ -1593,7 +1593,7 @@
     <row r="85">
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>大元の日報データは SharePoint の「2024定例会資料クラブ枠」にあります。リンク先を開き、右側にある当月列（例：2026-05）をコピーします。</t>
+          <t>大元の日報データは SharePoint の「2024定例会資料クラブ枠」にあります。リンク先を開き、当月分のデータをコピーします。</t>
         </is>
       </c>
     </row>
@@ -1607,19 +1607,61 @@
     <row r="97" ht="22" customHeight="1">
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>3-2. 先に前月列（1日平均）を数式→値にしておく</t>
+          <t>3-2. 「日報（件数）貼り付け用」に貼り付けて当月分を作る</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>メインExcelの 1日平均 シートで、前月列（例：5月度を作るなら 2026-04）を選択し、数式を「値」に変換しておきます。（＝前月分の数値を、計算式ではなく確定した数字として固定しておく作業です。）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="2" t="inlineStr">
+          <t>1日平均 シートは、別タブの「日報（件数）貼り付け用」と連携（数式参照）しています。横にある「日報（件数）貼り付け用」タブをクリックし、コピーした当月分をすべてコピー＆ペーストで貼り付けます。これが大元のデータになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>図：タブ：日報貼り付け用と1日平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>図：日報貼り付け用タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>貼り付けると、1日平均 シートの当月列にデータが流れ込み、当月分が出来上がります。当月の行（処理件数）が正しく入っているかを確認します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>図：日報に当月分を貼付</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>3-3. 前月分を「値」に置き換える（数値を固定する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>当月分が出来たのを確認してから、1日平均 シートの前月列（例：5月度を作るなら 2026-04）を選択し、数式を「値」に置き換えます。これで前月の数値が、以降の更新で変わらないように固定されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>【数式 ▶ 値 の変換手順】
 1. 前月列を選択してコピー（Ctrl + C）
@@ -1629,52 +1671,10 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>【注意】なぜ前月分を先に値にするの？ 1日平均 シートは別タブの「日報（件数）貼り付け用」と連携（数式参照）しています。前月分を値で固定しておかないと、次に当月分を貼り付けたときに前月の数値まで一緒に変わってしまうためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>図：タブ：日報貼り付け用と1日平均</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>3-3. 「日報（件数）貼り付け用」に当月分を貼り付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>横にある「日報（件数）貼り付け用」タブをクリックし、SharePointからコピーした当月分を、すべてコピー＆ペーストで貼り付けます。これが大元のデータになります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>図：日報貼り付け用タブ</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>貼り付け後、当月の行（処理件数）が反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>図：日報に当月分を貼付</t>
+    <row r="164">
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>【注意】なぜ前月分を値にするの？ 1日平均 は「日報（件数）貼り付け用」と連携しているため、前月分を値で固定しておかないと、次回以降データを更新したときに前月の数値まで一緒に変わってしまうためです。</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C889" s="4" t="inlineStr">
         <is>
-          <t>1日平均 は 日報（件数）貼り付け用 と連携している。貼り付け前に前月列を数式→値へ固定する（前月の数値が変わらないように）。</t>
+          <t>1日平均 は 日報（件数）貼り付け用 と連携している。当月分を貼り付けて当月分が出来たら、前月列を数式→値で固定する（前月の数値が変わらないように）。</t>
         </is>
       </c>
     </row>
@@ -2662,13 +2662,16 @@
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B691:F691"/>
     <mergeCell ref="B747:F747"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B628:F628"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B447:F447"/>
+    <mergeCell ref="B158:F158"/>
     <mergeCell ref="B477:F477"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B356:F356"/>
+    <mergeCell ref="B160:F160"/>
     <mergeCell ref="B449:F449"/>
     <mergeCell ref="B654:F654"/>
     <mergeCell ref="B663:F663"/>
@@ -2678,6 +2681,7 @@
     <mergeCell ref="B591:F591"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B662:F662"/>
+    <mergeCell ref="B134:F134"/>
     <mergeCell ref="B475:F475"/>
     <mergeCell ref="B882:F882"/>
     <mergeCell ref="B167:F167"/>
@@ -2685,6 +2689,7 @@
     <mergeCell ref="B630:F630"/>
     <mergeCell ref="B853:F853"/>
     <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B162:F162"/>
     <mergeCell ref="B780:F780"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B593:F593"/>
@@ -2720,24 +2725,20 @@
     <mergeCell ref="B451:F451"/>
     <mergeCell ref="B534:F534"/>
     <mergeCell ref="B656:F656"/>
-    <mergeCell ref="B137:F137"/>
     <mergeCell ref="B413:F413"/>
     <mergeCell ref="B776:F776"/>
     <mergeCell ref="B324:F324"/>
     <mergeCell ref="B899:F899"/>
-    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B164:F164"/>
     <mergeCell ref="B804:F804"/>
     <mergeCell ref="B222:F222"/>
     <mergeCell ref="B415:F415"/>
     <mergeCell ref="B560:F560"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B110:F110"/>
     <mergeCell ref="B859:F859"/>
     <mergeCell ref="B479:F479"/>
     <mergeCell ref="B380:F380"/>
     <mergeCell ref="B860:F860"/>
-    <mergeCell ref="B100:F100"/>
     <mergeCell ref="B327:F327"/>
     <mergeCell ref="B625:F625"/>
     <mergeCell ref="B165:F165"/>
@@ -2749,10 +2750,9 @@
     <mergeCell ref="B802:F802"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B660:F660"/>
-    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B132:F132"/>
     <mergeCell ref="B588:F588"/>
     <mergeCell ref="B563:F563"/>
-    <mergeCell ref="B112:F112"/>
     <mergeCell ref="B354:F354"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="B329:F329"/>

--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -298,7 +298,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="1238250"/>
@@ -323,7 +323,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3943350"/>
@@ -348,7 +348,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>134</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4171950"/>
@@ -1607,61 +1607,19 @@
     <row r="97" ht="22" customHeight="1">
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>3-2. 「日報（件数）貼り付け用」に貼り付けて当月分を作る</t>
+          <t>3-2. 前月分を「値」に置き換える（数値を固定する）</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1日平均 シートは、別タブの「日報（件数）貼り付け用」と連携（数式参照）しています。横にある「日報（件数）貼り付け用」タブをクリックし、コピーした当月分をすべてコピー＆ペーストで貼り付けます。これが大元のデータになります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>図：タブ：日報貼り付け用と1日平均</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>図：日報貼り付け用タブ</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>貼り付けると、1日平均 シートの当月列にデータが流れ込み、当月分が出来上がります。当月の行（処理件数）が正しく入っているかを確認します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>図：日報に当月分を貼付</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="22" customHeight="1">
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>3-3. 前月分を「値」に置き換える（数値を固定する）</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>当月分が出来たのを確認してから、1日平均 シートの前月列（例：5月度を作るなら 2026-04）を選択し、数式を「値」に置き換えます。これで前月の数値が、以降の更新で変わらないように固定されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="B163" s="2" t="inlineStr">
+          <t>まず最初に、1日平均 シートの前月列（例：5月度を作るなら 2026-04）を選択し、数式を「値」に置き換えます。これで前月の数値が、このあとの貼り付けや以降の更新で変わらないように固定されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>【数式 ▶ 値 の変換手順】
 1. 前月列を選択してコピー（Ctrl + C）
@@ -1671,10 +1629,52 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="B164" s="5" t="inlineStr">
-        <is>
-          <t>【注意】なぜ前月分を値にするの？ 1日平均 は「日報（件数）貼り付け用」と連携しているため、前月分を値で固定しておかないと、次回以降データを更新したときに前月の数値まで一緒に変わってしまうためです。</t>
+    <row r="101">
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>【注意】なぜ最初に値にするの？ 1日平均 は別タブの「日報（件数）貼り付け用」と連携（数式参照）しているため、先に前月分を値で固定しておかないと、次に当月分を貼り付けたときに前月の数値まで一緒に変わってしまうためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>図：タブ：日報貼り付け用と1日平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>3-3. 「日報（件数）貼り付け用」に当月分を貼り付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>横にある「日報（件数）貼り付け用」タブをクリックし、コピーした当月分をすべてコピー＆ペーストで貼り付けます。これが大元のデータになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>図：日報貼り付け用タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>貼り付けると、1日平均 シートの当月列にデータが反映され、当月分が出来上がります。当月の行（処理件数）が正しく入っているかを確認します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>図：日報に当月分を貼付</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C889" s="4" t="inlineStr">
         <is>
-          <t>1日平均 は 日報（件数）貼り付け用 と連携している。当月分を貼り付けて当月分が出来たら、前月列を数式→値で固定する（前月の数値が変わらないように）。</t>
+          <t>1日平均 は 日報（件数）貼り付け用 と連携している。先に前月列を数式→値で固定してから、当月分を貼り付ける（前月の数値が変わらないように）。</t>
         </is>
       </c>
     </row>
@@ -2662,16 +2662,13 @@
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B691:F691"/>
     <mergeCell ref="B747:F747"/>
-    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B628:F628"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B447:F447"/>
-    <mergeCell ref="B158:F158"/>
     <mergeCell ref="B477:F477"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B356:F356"/>
-    <mergeCell ref="B160:F160"/>
     <mergeCell ref="B449:F449"/>
     <mergeCell ref="B654:F654"/>
     <mergeCell ref="B663:F663"/>
@@ -2681,7 +2678,6 @@
     <mergeCell ref="B591:F591"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B662:F662"/>
-    <mergeCell ref="B134:F134"/>
     <mergeCell ref="B475:F475"/>
     <mergeCell ref="B882:F882"/>
     <mergeCell ref="B167:F167"/>
@@ -2689,7 +2685,6 @@
     <mergeCell ref="B630:F630"/>
     <mergeCell ref="B853:F853"/>
     <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B162:F162"/>
     <mergeCell ref="B780:F780"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B593:F593"/>
@@ -2725,20 +2720,24 @@
     <mergeCell ref="B451:F451"/>
     <mergeCell ref="B534:F534"/>
     <mergeCell ref="B656:F656"/>
+    <mergeCell ref="B137:F137"/>
     <mergeCell ref="B413:F413"/>
     <mergeCell ref="B776:F776"/>
     <mergeCell ref="B324:F324"/>
     <mergeCell ref="B899:F899"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B139:F139"/>
     <mergeCell ref="B804:F804"/>
     <mergeCell ref="B222:F222"/>
     <mergeCell ref="B415:F415"/>
     <mergeCell ref="B560:F560"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B110:F110"/>
     <mergeCell ref="B859:F859"/>
     <mergeCell ref="B479:F479"/>
     <mergeCell ref="B380:F380"/>
     <mergeCell ref="B860:F860"/>
+    <mergeCell ref="B100:F100"/>
     <mergeCell ref="B327:F327"/>
     <mergeCell ref="B625:F625"/>
     <mergeCell ref="B165:F165"/>
@@ -2750,9 +2749,10 @@
     <mergeCell ref="B802:F802"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B660:F660"/>
-    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B588:F588"/>
     <mergeCell ref="B563:F563"/>
+    <mergeCell ref="B112:F112"/>
     <mergeCell ref="B354:F354"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="B329:F329"/>

--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -273,35 +273,35 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7429500" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="1447800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>101</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7429500" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1586,40 +1586,19 @@
     <row r="83" ht="22" customHeight="1">
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>3-1. 元データを取り込む</t>
+          <t>3-1. 前月分を「値」に置き換える（数値を固定する）</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>大元の日報データは SharePoint の「2024定例会資料クラブ枠」にあります。リンク先を開き、当月分のデータをコピーします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>図：1日平均シート</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="22" customHeight="1">
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>3-2. 前月分を「値」に置き換える（数値を固定する）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="2" t="inlineStr">
-        <is>
           <t>まず最初に、1日平均 シートの前月列（例：5月度を作るなら 2026-04）を選択し、数式を「値」に置き換えます。これで前月の数値が、このあとの貼り付けや以降の更新で変わらないように固定されます。</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="2" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>【数式 ▶ 値 の変換手順】
 1. 前月列を選択してコピー（Ctrl + C）
@@ -1629,17 +1608,38 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="5" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>【注意】なぜ最初に値にするの？ 1日平均 は別タブの「日報（件数）貼り付け用」と連携（数式参照）しているため、先に前月分を値で固定しておかないと、次に当月分を貼り付けたときに前月の数値まで一緒に変わってしまうためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>図：タブ：日報貼り付け用と1日平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>3-2. 元データを取り込む</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>大元の日報データは SharePoint の「2024定例会資料クラブ枠」にあります。リンク先を開き、当月分のデータをコピーします。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>図：タブ：日報貼り付け用と1日平均</t>
+          <t>図：1日平均シート</t>
         </is>
       </c>
     </row>
@@ -2680,13 +2680,14 @@
     <mergeCell ref="B662:F662"/>
     <mergeCell ref="B475:F475"/>
     <mergeCell ref="B882:F882"/>
+    <mergeCell ref="B96:F96"/>
     <mergeCell ref="B167:F167"/>
     <mergeCell ref="B503:F503"/>
     <mergeCell ref="B630:F630"/>
     <mergeCell ref="B853:F853"/>
+    <mergeCell ref="B98:F98"/>
     <mergeCell ref="B82:F82"/>
     <mergeCell ref="B780:F780"/>
-    <mergeCell ref="B99:F99"/>
     <mergeCell ref="B593:F593"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B658:F658"/>
@@ -2717,6 +2718,7 @@
     <mergeCell ref="B274:F274"/>
     <mergeCell ref="B191:F191"/>
     <mergeCell ref="B249:F249"/>
+    <mergeCell ref="B87:F87"/>
     <mergeCell ref="B451:F451"/>
     <mergeCell ref="B534:F534"/>
     <mergeCell ref="B656:F656"/>
@@ -2748,8 +2750,8 @@
     <mergeCell ref="B562:F562"/>
     <mergeCell ref="B802:F802"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="B660:F660"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B588:F588"/>
     <mergeCell ref="B563:F563"/>
     <mergeCell ref="B112:F112"/>
@@ -2761,12 +2763,10 @@
     <mergeCell ref="B565:F565"/>
     <mergeCell ref="B745:F745"/>
     <mergeCell ref="B501:F501"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B695:F695"/>
     <mergeCell ref="B778:F778"/>
     <mergeCell ref="B330:F330"/>
-    <mergeCell ref="B97:F97"/>
     <mergeCell ref="B526:F526"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -1940,14 +1940,14 @@
     <row r="477" ht="22" customHeight="1">
       <c r="B477" s="8" t="inlineStr">
         <is>
-          <t>5-4. 件数の根拠はOutlookで確認</t>
+          <t>5-4. 件数は福島さんが入力（経緯はOutlookで確認）</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>八神の件数は Outlookのメールから集計しています。件数が多い・少ないと感じたら、該当メールを開いて内訳（理由）を確認できます。</t>
+          <t>八神の件数は、自分でメールから集計するのではなく、福島さんが毎週火曜日にセルアウト担当をするときに入力してくれています。そのため、基本的にこちらで数字を作る必要はありません。件数が多い・少ない、またイレギュラーがあった月は、該当のOutlookメールで内訳や経緯を確認できます。</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
     <row r="503">
       <c r="B503" s="5" t="inlineStr">
         <is>
-          <t>【補足】件数が「9件」などになっている場合、その理由はこのメールで確認できます（多い月は背景を紐解いておくとコメントが書きやすくなります）。</t>
+          <t>【補足】イレギュラー対応の例：2026年5月は週の始めが祝日だったため、火曜ではなく金曜日にイレギュラー対応しています（その旨のコメントが入っています）。件数が「9件」など気になるときも、メールで理由を確認できます（多い月は背景を紐解いておくとコメントが書きやすくなります）。</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C894" s="4" t="inlineStr">
         <is>
-          <t>八神・メール・サポートの件数は Outlook側に根拠がある。多い月は理由を確認。</t>
+          <t>八神の件数は福島さんが毎週火曜のセルアウト担当時に入力（メール・サポートはOutlookに根拠）。多い月・イレギュラーは理由を確認。</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F904" s="4" t="inlineStr">
         <is>
-          <t>行3〜6（一括/買取/長期/短期）。件数はOutlook集計</t>
+          <t>行3〜6（一括/買取/長期/短期）。件数は福島さんが毎週火曜のセルアウト担当時に入力</t>
         </is>
       </c>
     </row>

--- a/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
+++ b/docs/定例会資料マニュアル/定例会資料の作り方.xlsx
@@ -723,7 +723,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>565</row>
+      <row>566</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3914775"/>
@@ -748,7 +748,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>596</row>
+      <row>597</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="5076825"/>
@@ -773,7 +773,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>630</row>
+      <row>631</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4076700"/>
@@ -798,7 +798,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>665</row>
+      <row>666</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4391025"/>
@@ -823,7 +823,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>695</row>
+      <row>696</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4162425"/>
@@ -848,7 +848,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>721</row>
+      <row>722</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4086225"/>
@@ -873,7 +873,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>749</row>
+      <row>750</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4581525"/>
@@ -898,7 +898,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>780</row>
+      <row>781</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3676650"/>
@@ -923,7 +923,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>804</row>
+      <row>805</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3886200"/>
@@ -948,7 +948,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>829</row>
+      <row>830</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="4105275"/>
@@ -973,7 +973,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>860</row>
+      <row>861</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7429500" cy="3800475"/>
@@ -1286,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F910"/>
+  <dimension ref="B2:F911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2010,480 +2010,460 @@
     <row r="562">
       <c r="B562" s="5" t="inlineStr">
         <is>
-          <t>【用語】「返却通知書（代理）」は、正式には「返却・使用通知書」というタイトルの書類です。該当データはメールブランチの後ろにあります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="563" ht="22" customHeight="1">
-      <c r="B563" s="8" t="inlineStr">
+          <t>【用語】「返却通知書（代理）」は、正式には「返却・使用通知書」というタイトルの書類です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" s="5" t="inlineStr">
+        <is>
+          <t>【場所】メールブランチはロッカーの中の一番上に格納されています。中身は日付ごとに管理されていて、目的の返却・使用通知書はメールブランチの一番後ろあたりにあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="22" customHeight="1">
+      <c r="B564" s="8" t="inlineStr">
         <is>
           <t>6-2. グラフをPowerPointへ</t>
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="B565" s="2" t="inlineStr">
+    <row r="566">
+      <c r="B566" s="2" t="inlineStr">
         <is>
           <t>グラフをスライド6へコピーし、コメントを記入します。</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="B588" s="7" t="inlineStr">
+    <row r="589">
+      <c r="B589" s="7" t="inlineStr">
         <is>
           <t>図：スライド6：サポート</t>
         </is>
       </c>
     </row>
-    <row r="591" ht="30" customHeight="1">
-      <c r="B591" s="1" t="inlineStr">
+    <row r="592" ht="30" customHeight="1">
+      <c r="B592" s="1" t="inlineStr">
         <is>
           <t>7. スライド7：メール依頼</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="B593" s="2" t="inlineStr">
+    <row r="594">
+      <c r="B594" s="2" t="inlineStr">
         <is>
           <t>メール依頼（その他／代理店／Cordis本社／営業）の当月件数を表示します。</t>
         </is>
       </c>
     </row>
-    <row r="594" ht="22" customHeight="1">
-      <c r="B594" s="8" t="inlineStr">
+    <row r="595" ht="22" customHeight="1">
+      <c r="B595" s="8" t="inlineStr">
         <is>
           <t>7-1. メール依頼ファイルを開く</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="B596" s="2" t="inlineStr">
+    <row r="597">
+      <c r="B597" s="2" t="inlineStr">
         <is>
           <t>2026年度メール依頼.xlsx を開き、当月タブ（例：メール2026.5）のグラフを確認します。</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="B625" s="7" t="inlineStr">
+    <row r="626">
+      <c r="B626" s="7" t="inlineStr">
         <is>
           <t>図：メール依頼シート</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="B627" s="5" t="inlineStr">
+    <row r="628">
+      <c r="B628" s="5" t="inlineStr">
         <is>
           <t>【補足】メール依頼について：ここは原則いじるものはありません。集計は関さんがまとめてくれています。件数が多いときは「なぜ多いのか？」を紐解いておく必要があります。</t>
         </is>
       </c>
     </row>
-    <row r="628" ht="22" customHeight="1">
-      <c r="B628" s="8" t="inlineStr">
+    <row r="629" ht="22" customHeight="1">
+      <c r="B629" s="8" t="inlineStr">
         <is>
           <t>7-2. 件数の根拠はOutlookで確認</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="B630" s="2" t="inlineStr">
+    <row r="631">
+      <c r="B631" s="2" t="inlineStr">
         <is>
           <t>件数はOutlookで集計しています。必要に応じて該当メールで内訳を確認します。</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="B654" s="7" t="inlineStr">
+    <row r="655">
+      <c r="B655" s="7" t="inlineStr">
         <is>
           <t>図：Outlook：メール依頼</t>
         </is>
       </c>
     </row>
-    <row r="656" ht="22" customHeight="1">
-      <c r="B656" s="8" t="inlineStr">
+    <row r="657" ht="22" customHeight="1">
+      <c r="B657" s="8" t="inlineStr">
         <is>
           <t>7-3. グラフをPowerPointへ</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="B658" s="2" t="inlineStr">
+    <row r="659">
+      <c r="B659" s="2" t="inlineStr">
         <is>
           <t>グラフをスライド7へコピーし、コメントを記入します。</t>
         </is>
       </c>
     </row>
-    <row r="660" ht="30" customHeight="1">
-      <c r="B660" s="1" t="inlineStr">
+    <row r="661" ht="30" customHeight="1">
+      <c r="B661" s="1" t="inlineStr">
         <is>
           <t>8. スライド8：電話応対（グラフ＋右上の集計表）</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="B662" s="2" t="inlineStr">
+    <row r="663">
+      <c r="B663" s="2" t="inlineStr">
         <is>
           <t>当月の日別 受信／発信件数の棒グラフと、右上の集計表（前月比つき）を更新します。</t>
         </is>
       </c>
     </row>
-    <row r="663" ht="22" customHeight="1">
-      <c r="B663" s="8" t="inlineStr">
+    <row r="664" ht="22" customHeight="1">
+      <c r="B664" s="8" t="inlineStr">
         <is>
           <t>8-1. 受発信の元データを用意する</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="B665" s="2" t="inlineStr">
+    <row r="666">
+      <c r="B666" s="2" t="inlineStr">
         <is>
           <t>その月の 202605受発信.xlsx（受信件数／発信件数の日別データ）を開きます。</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="B691" s="7" t="inlineStr">
+    <row r="692">
+      <c r="B692" s="7" t="inlineStr">
         <is>
           <t>図：受発信：元データ</t>
         </is>
       </c>
     </row>
-    <row r="693" ht="22" customHeight="1">
-      <c r="B693" s="8" t="inlineStr">
+    <row r="694" ht="22" customHeight="1">
+      <c r="B694" s="8" t="inlineStr">
         <is>
           <t>8-2. メインExcelの「電話」タブに貼り付ける</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="B695" s="2" t="inlineStr">
+    <row r="696">
+      <c r="B696" s="2" t="inlineStr">
         <is>
           <t>メインExcelの 電話 タブを開きます。貼り付け前は前月のデータが入っています。</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="B719" s="7" t="inlineStr">
+    <row r="720">
+      <c r="B720" s="7" t="inlineStr">
         <is>
           <t>図：電話タブ：前月状態</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="B721" s="2" t="inlineStr">
+    <row r="722">
+      <c r="B722" s="2" t="inlineStr">
         <is>
           <t>受発信データを 電話 タブに貼り付けると、グラフと数値が当月に切り替わります。</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="B745" s="7" t="inlineStr">
+    <row r="746">
+      <c r="B746" s="7" t="inlineStr">
         <is>
           <t>図：電話タブ：当月貼付</t>
         </is>
       </c>
     </row>
-    <row r="747" ht="22" customHeight="1">
-      <c r="B747" s="8" t="inlineStr">
+    <row r="748" ht="22" customHeight="1">
+      <c r="B748" s="8" t="inlineStr">
         <is>
           <t>8-3. 平均と集計表を更新する</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="B749" s="2" t="inlineStr">
+    <row r="750">
+      <c r="B750" s="2" t="inlineStr">
         <is>
           <t>・平均件数＝合計 ÷ 稼働日数（例：=C32/18 のように、合計を稼働日数で割る）で計算します。・右上の集計表（N35:Q38）には、当月・前月・前月比（%）が入ります。</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="B776" s="7" t="inlineStr">
+    <row r="777">
+      <c r="B777" s="7" t="inlineStr">
         <is>
           <t>図：電話：平均算出と集計表</t>
         </is>
       </c>
     </row>
-    <row r="778" ht="22" customHeight="1">
-      <c r="B778" s="8" t="inlineStr">
+    <row r="779" ht="22" customHeight="1">
+      <c r="B779" s="8" t="inlineStr">
         <is>
           <t>8-4. グラフをPowerPointへ（軸の最大値に注意）</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="B780" s="2" t="inlineStr">
+    <row r="781">
+      <c r="B781" s="2" t="inlineStr">
         <is>
           <t>グラフをスライド8へコピーします。</t>
         </is>
       </c>
     </row>
-    <row r="802">
-      <c r="B802" s="7" t="inlineStr">
+    <row r="803">
+      <c r="B803" s="7" t="inlineStr">
         <is>
           <t>図：PPT電話：軸調整1</t>
         </is>
       </c>
     </row>
-    <row r="804">
-      <c r="B804" s="5" t="inlineStr">
+    <row r="805">
+      <c r="B805" s="5" t="inlineStr">
         <is>
           <t>【注意】縦軸の最大値を月に合わせて手調整します。件数に応じて、70件以下の月なら最大を50にするなど、見やすい高さに直してください。</t>
         </is>
       </c>
     </row>
-    <row r="827">
-      <c r="B827" s="7" t="inlineStr">
+    <row r="828">
+      <c r="B828" s="7" t="inlineStr">
         <is>
           <t>図：PPT電話：軸調整2</t>
         </is>
       </c>
     </row>
-    <row r="829">
-      <c r="B829" s="2" t="inlineStr">
+    <row r="830">
+      <c r="B830" s="2" t="inlineStr">
         <is>
           <t>集計表も合わせて貼り付け／更新し、コメントを記入すれば完成です。</t>
         </is>
       </c>
     </row>
-    <row r="853">
-      <c r="B853" s="7" t="inlineStr">
+    <row r="854">
+      <c r="B854" s="7" t="inlineStr">
         <is>
           <t>図：スライド8：電話完成</t>
         </is>
       </c>
     </row>
-    <row r="856" ht="30" customHeight="1">
-      <c r="B856" s="1" t="inlineStr">
+    <row r="857" ht="30" customHeight="1">
+      <c r="B857" s="1" t="inlineStr">
         <is>
           <t>9. 仕上げ：保存</t>
         </is>
       </c>
     </row>
-    <row r="858">
-      <c r="B858" s="2" t="inlineStr">
+    <row r="859">
+      <c r="B859" s="2" t="inlineStr">
         <is>
           <t>すべてのスライドを更新し、コメントを記入したら、ネットワークフォルダに保存します。</t>
         </is>
       </c>
     </row>
-    <row r="859">
-      <c r="B859" s="6" t="inlineStr">
+    <row r="860">
+      <c r="B860" s="6" t="inlineStr">
         <is>
           <t>…\16_定例会\2026\</t>
         </is>
       </c>
     </row>
-    <row r="860">
-      <c r="B860" s="2" t="inlineStr">
+    <row r="861">
+      <c r="B861" s="2" t="inlineStr">
         <is>
           <t>・pptx（編集用）と PDF（配布用）の両方で保存します。・ファイル名は コーディスジャパン定例会資料_2026年○月度 の形式に合わせます。</t>
         </is>
       </c>
     </row>
-    <row r="882">
-      <c r="B882" s="7" t="inlineStr">
+    <row r="883">
+      <c r="B883" s="7" t="inlineStr">
         <is>
           <t>図：ネットワーク保存ダイアログ</t>
         </is>
       </c>
     </row>
-    <row r="885" ht="30" customHeight="1">
-      <c r="B885" s="1" t="inlineStr">
+    <row r="886" ht="30" customHeight="1">
+      <c r="B886" s="1" t="inlineStr">
         <is>
           <t>10. つまずきやすいポイント（チェックリスト）</t>
         </is>
       </c>
     </row>
-    <row r="887">
-      <c r="B887" s="3" t="inlineStr">
+    <row r="888">
+      <c r="B888" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C887" s="3" t="inlineStr">
+      <c r="C888" s="3" t="inlineStr">
         <is>
           <t>注意点</t>
-        </is>
-      </c>
-    </row>
-    <row r="888">
-      <c r="B888" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C888" s="4" t="inlineStr">
-        <is>
-          <t>月度の書き換えは最初に。アジェンダ・タイトルの「○月度」を当月へ。</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="B889" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C889" s="4" t="inlineStr">
         <is>
-          <t>1日平均 は 日報（件数）貼り付け用 と連携している。先に前月列を数式→値で固定してから、当月分を貼り付ける（前月の数値が変わらないように）。</t>
+          <t>月度の書き換えは最初に。アジェンダ・タイトルの「○月度」を当月へ。</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="B890" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C890" s="4" t="inlineStr">
         <is>
-          <t>日別グラフは土日祝（0件）の列を非表示（削除しない）。「0だから非表示」ではなく「土日祝だから非表示」。</t>
+          <t>1日平均 は 日報（件数）貼り付け用 と連携している。先に前月列を数式→値で固定してから、当月分を貼り付ける（前月の数値が変わらないように）。</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="B891" s="4" t="inlineStr">
         <is>
-          <t>3b</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C891" s="4" t="inlineStr">
         <is>
-          <t>八神セルアウトの 一括 行の空欄には手動で 0 を入れる（空欄のままだとグラフ・合計に反映されない）。</t>
+          <t>日別グラフは土日祝（0件）の列を非表示（削除しない）。「0だから非表示」ではなく「土日祝だから非表示」。</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="B892" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3b</t>
         </is>
       </c>
       <c r="C892" s="4" t="inlineStr">
         <is>
-          <t>電話の平均は 合計 ÷ 稼働日数。日数を間違えると平均がずれる。</t>
+          <t>八神セルアウトの 一括 行の空欄には手動で 0 を入れる（空欄のままだとグラフ・合計に反映されない）。</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="B893" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C893" s="4" t="inlineStr">
         <is>
-          <t>電話グラフの縦軸の最大値は手調整（70件以下なら50など）。</t>
+          <t>電話の平均は 合計 ÷ 稼働日数。日数を間違えると平均がずれる。</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="B894" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C894" s="4" t="inlineStr">
         <is>
-          <t>八神の件数は福島さんが毎週火曜のセルアウト担当時に入力（メール・サポートはOutlookに根拠）。多い月・イレギュラーは理由を確認。</t>
+          <t>電話グラフの縦軸の最大値は手調整（70件以下なら50など）。</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="B895" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C895" s="4" t="inlineStr">
         <is>
-          <t>グラフをPowerPointへ貼るときは、系列の順番・色が崩れていないかを確認（特にスライド3の複合グラフ）。</t>
+          <t>八神の件数は福島さんが毎週火曜のセルアウト担当時に入力（メール・サポートはOutlookに根拠）。多い月・イレギュラーは理由を確認。</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="B896" s="4" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C896" s="4" t="inlineStr">
+        <is>
+          <t>グラフをPowerPointへ貼るときは、系列の順番・色が崩れていないかを確認（特にスライド3の複合グラフ）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="B897" s="4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C896" s="4" t="inlineStr">
+      <c r="C897" s="4" t="inlineStr">
         <is>
           <t>最後は pptxとPDFの両方をネットワークに保存。</t>
         </is>
       </c>
     </row>
-    <row r="899" ht="30" customHeight="1">
-      <c r="B899" s="1" t="inlineStr">
+    <row r="900" ht="30" customHeight="1">
+      <c r="B900" s="1" t="inlineStr">
         <is>
           <t>付録：データソース対応表</t>
         </is>
       </c>
     </row>
-    <row r="901">
-      <c r="B901" s="3" t="inlineStr">
+    <row r="902">
+      <c r="B902" s="3" t="inlineStr">
         <is>
           <t>スライド</t>
         </is>
       </c>
-      <c r="C901" s="3" t="inlineStr">
+      <c r="C902" s="3" t="inlineStr">
         <is>
           <t>グラフ／表</t>
         </is>
       </c>
-      <c r="D901" s="3" t="inlineStr">
+      <c r="D902" s="3" t="inlineStr">
         <is>
           <t>元ファイル</t>
         </is>
       </c>
-      <c r="E901" s="3" t="inlineStr">
+      <c r="E902" s="3" t="inlineStr">
         <is>
           <t>シート</t>
         </is>
       </c>
-      <c r="F901" s="3" t="inlineStr">
+      <c r="F902" s="3" t="inlineStr">
         <is>
           <t>参照範囲・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="902">
-      <c r="B902" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C902" s="4" t="inlineStr">
-        <is>
-          <t>月別1日平均（棒＋折れ線）</t>
-        </is>
-      </c>
-      <c r="D902" s="4" t="inlineStr">
-        <is>
-          <t>メインExcel</t>
-        </is>
-      </c>
-      <c r="E902" s="4" t="inlineStr">
-        <is>
-          <t>1日平均</t>
-        </is>
-      </c>
-      <c r="F902" s="4" t="inlineStr">
-        <is>
-          <t>行2〜10、直近13ヶ月。横軸＝日付(yyyy-mm)</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="B903" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C903" s="4" t="inlineStr">
         <is>
-          <t>日別処理（積み上げ棒）</t>
+          <t>月別1日平均（棒＋折れ線）</t>
         </is>
       </c>
       <c r="D903" s="4" t="inlineStr">
@@ -2493,211 +2473,245 @@
       </c>
       <c r="E903" s="4" t="inlineStr">
         <is>
-          <t>新）日別処理</t>
+          <t>1日平均</t>
         </is>
       </c>
       <c r="F903" s="4" t="inlineStr">
         <is>
-          <t>行3〜7。稼働日のみ。横軸＝日付＋曜日</t>
+          <t>行2〜10、直近13ヶ月。横軸＝日付(yyyy-mm)</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="B904" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C904" s="4" t="inlineStr">
         <is>
-          <t>八神セルアウト</t>
+          <t>日別処理（積み上げ棒）</t>
         </is>
       </c>
       <c r="D904" s="4" t="inlineStr">
         <is>
-          <t>★八神sellout集計</t>
+          <t>メインExcel</t>
         </is>
       </c>
       <c r="E904" s="4" t="inlineStr">
         <is>
-          <t>2026.5 等</t>
+          <t>新）日別処理</t>
         </is>
       </c>
       <c r="F904" s="4" t="inlineStr">
         <is>
-          <t>行3〜6（一括/買取/長期/短期）。件数は福島さんが毎週火曜のセルアウト担当時に入力</t>
+          <t>行3〜7。稼働日のみ。横軸＝日付＋曜日</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="B905" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C905" s="4" t="inlineStr">
         <is>
-          <t>サポート業務</t>
+          <t>八神セルアウト</t>
         </is>
       </c>
       <c r="D905" s="4" t="inlineStr">
         <is>
-          <t>2026年度サポートグラフ</t>
+          <t>★八神sellout集計</t>
         </is>
       </c>
       <c r="E905" s="4" t="inlineStr">
         <is>
-          <t>サポート2026.5 等</t>
+          <t>2026.5 等</t>
         </is>
       </c>
       <c r="F905" s="4" t="inlineStr">
         <is>
-          <t>行3〜7（補充・使用報告書/返却通知書×2/サンプル/赤伝）</t>
+          <t>行3〜6（一括/買取/長期/短期）。件数は福島さんが毎週火曜のセルアウト担当時に入力</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="B906" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C906" s="4" t="inlineStr">
         <is>
-          <t>メール依頼</t>
+          <t>サポート業務</t>
         </is>
       </c>
       <c r="D906" s="4" t="inlineStr">
         <is>
-          <t>2026年度メール依頼</t>
+          <t>2026年度サポートグラフ</t>
         </is>
       </c>
       <c r="E906" s="4" t="inlineStr">
         <is>
-          <t>メール2026.5 等</t>
+          <t>サポート2026.5 等</t>
         </is>
       </c>
       <c r="F906" s="4" t="inlineStr">
         <is>
-          <t>行3〜6（その他/代理店/Cordis本社/営業）。件数はOutlook集計</t>
+          <t>行3〜7（補充・使用報告書/返却通知書×2/サンプル/赤伝）</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="B907" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C907" s="4" t="inlineStr">
         <is>
-          <t>電話応対（棒）＋集計表</t>
+          <t>メール依頼</t>
         </is>
       </c>
       <c r="D907" s="4" t="inlineStr">
         <is>
-          <t>メインExcel</t>
+          <t>2026年度メール依頼</t>
         </is>
       </c>
       <c r="E907" s="4" t="inlineStr">
         <is>
-          <t>電話</t>
+          <t>メール2026.5 等</t>
         </is>
       </c>
       <c r="F907" s="4" t="inlineStr">
         <is>
-          <t>グラフ:C/D列、表:N35:Q38。元データ=202605受発信.xlsx</t>
+          <t>行3〜6（その他/代理店/Cordis本社/営業）。件数はOutlook集計</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="B908" s="4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C908" s="4" t="inlineStr">
+        <is>
+          <t>電話応対（棒）＋集計表</t>
+        </is>
+      </c>
+      <c r="D908" s="4" t="inlineStr">
+        <is>
+          <t>メインExcel</t>
+        </is>
+      </c>
+      <c r="E908" s="4" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="F908" s="4" t="inlineStr">
+        <is>
+          <t>グラフ:C/D列、表:N35:Q38。元データ=202605受発信.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="B909" s="4" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C908" s="4" t="inlineStr">
+      <c r="C909" s="4" t="inlineStr">
         <is>
           <t>処理ミス（PPM・折れ線）</t>
         </is>
       </c>
-      <c r="D908" s="4" t="inlineStr">
+      <c r="D909" s="4" t="inlineStr">
         <is>
           <t>メインExcel</t>
         </is>
       </c>
-      <c r="E908" s="4" t="inlineStr">
+      <c r="E909" s="4" t="inlineStr">
         <is>
           <t>ミス2024</t>
         </is>
       </c>
-      <c r="F908" s="4" t="inlineStr">
+      <c r="F909" s="4" t="inlineStr">
         <is>
           <t>横軸＝月、系列＝前年/当年</t>
         </is>
       </c>
     </row>
-    <row r="910">
-      <c r="B910" s="5" t="inlineStr">
+    <row r="911">
+      <c r="B911" s="5" t="inlineStr">
         <is>
           <t>祝日：メインExcelの 向う数年の祝日 シートに祝日リストがあり、稼働日の判定に使います。電話の元データ：202605受発信.xlsx を 電話 タブに貼り付けてから使います。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="122">
-    <mergeCell ref="B693:F693"/>
+  <mergeCells count="123">
+    <mergeCell ref="B566:F566"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B666:F666"/>
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B721:F721"/>
     <mergeCell ref="B276:F276"/>
+    <mergeCell ref="B631:F631"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B665:F665"/>
+    <mergeCell ref="B592:F592"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B779:F779"/>
+    <mergeCell ref="B828:F828"/>
     <mergeCell ref="B529:F529"/>
-    <mergeCell ref="B827:F827"/>
     <mergeCell ref="B594:F594"/>
     <mergeCell ref="B532:F532"/>
+    <mergeCell ref="B626:F626"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B691:F691"/>
-    <mergeCell ref="B747:F747"/>
     <mergeCell ref="B628:F628"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B447:F447"/>
     <mergeCell ref="B477:F477"/>
+    <mergeCell ref="B692:F692"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B356:F356"/>
     <mergeCell ref="B449:F449"/>
-    <mergeCell ref="B654:F654"/>
+    <mergeCell ref="B694:F694"/>
+    <mergeCell ref="B781:F781"/>
     <mergeCell ref="B663:F663"/>
-    <mergeCell ref="B719:F719"/>
     <mergeCell ref="B227:F227"/>
     <mergeCell ref="B531:F531"/>
-    <mergeCell ref="B591:F591"/>
     <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B662:F662"/>
     <mergeCell ref="B475:F475"/>
-    <mergeCell ref="B882:F882"/>
+    <mergeCell ref="B655:F655"/>
     <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B720:F720"/>
     <mergeCell ref="B167:F167"/>
     <mergeCell ref="B503:F503"/>
-    <mergeCell ref="B630:F630"/>
-    <mergeCell ref="B853:F853"/>
+    <mergeCell ref="B657:F657"/>
     <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B803:F803"/>
+    <mergeCell ref="B883:F883"/>
     <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B780:F780"/>
-    <mergeCell ref="B593:F593"/>
+    <mergeCell ref="B696:F696"/>
+    <mergeCell ref="B854:F854"/>
+    <mergeCell ref="B664:F664"/>
+    <mergeCell ref="B746:F746"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B658:F658"/>
-    <mergeCell ref="B829:F829"/>
+    <mergeCell ref="B900:F900"/>
     <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B595:F595"/>
+    <mergeCell ref="B722:F722"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B251:F251"/>
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B296:F296"/>
+    <mergeCell ref="B659:F659"/>
+    <mergeCell ref="B830:F830"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B271:F271"/>
     <mergeCell ref="B218:F218"/>
@@ -2705,30 +2719,27 @@
     <mergeCell ref="B416:F416"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B321:F321"/>
-    <mergeCell ref="B596:F596"/>
-    <mergeCell ref="B885:F885"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B273:F273"/>
-    <mergeCell ref="B749:F749"/>
+    <mergeCell ref="B857:F857"/>
     <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B856:F856"/>
+    <mergeCell ref="B748:F748"/>
+    <mergeCell ref="B911:F911"/>
     <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B858:F858"/>
     <mergeCell ref="B225:F225"/>
     <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B750:F750"/>
     <mergeCell ref="B191:F191"/>
     <mergeCell ref="B249:F249"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="B451:F451"/>
     <mergeCell ref="B534:F534"/>
-    <mergeCell ref="B656:F656"/>
+    <mergeCell ref="B805:F805"/>
     <mergeCell ref="B137:F137"/>
     <mergeCell ref="B413:F413"/>
-    <mergeCell ref="B776:F776"/>
+    <mergeCell ref="B589:F589"/>
     <mergeCell ref="B324:F324"/>
-    <mergeCell ref="B899:F899"/>
     <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B804:F804"/>
     <mergeCell ref="B222:F222"/>
     <mergeCell ref="B415:F415"/>
     <mergeCell ref="B560:F560"/>
@@ -2738,34 +2749,31 @@
     <mergeCell ref="B859:F859"/>
     <mergeCell ref="B479:F479"/>
     <mergeCell ref="B380:F380"/>
+    <mergeCell ref="B777:F777"/>
+    <mergeCell ref="B886:F886"/>
     <mergeCell ref="B860:F860"/>
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="B327:F327"/>
-    <mergeCell ref="B625:F625"/>
     <mergeCell ref="B165:F165"/>
-    <mergeCell ref="B910:F910"/>
+    <mergeCell ref="B861:F861"/>
     <mergeCell ref="B382:F382"/>
     <mergeCell ref="B326:F326"/>
     <mergeCell ref="B220:F220"/>
     <mergeCell ref="B562:F562"/>
-    <mergeCell ref="B802:F802"/>
+    <mergeCell ref="B661:F661"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B660:F660"/>
-    <mergeCell ref="B588:F588"/>
+    <mergeCell ref="B597:F597"/>
     <mergeCell ref="B563:F563"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B354:F354"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="B329:F329"/>
-    <mergeCell ref="B627:F627"/>
     <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B565:F565"/>
-    <mergeCell ref="B745:F745"/>
     <mergeCell ref="B501:F501"/>
+    <mergeCell ref="B564:F564"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B695:F695"/>
-    <mergeCell ref="B778:F778"/>
+    <mergeCell ref="B629:F629"/>
     <mergeCell ref="B330:F330"/>
     <mergeCell ref="B526:F526"/>
   </mergeCells>
